--- a/summary_stats/chuuchuu_summary_2025_06.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_06.xlsx
@@ -1454,25 +1454,25 @@
         <v>132</v>
       </c>
       <c r="N13" t="n">
-        <v>1357</v>
+        <v>1304</v>
       </c>
       <c r="O13" t="n">
-        <v>1182</v>
+        <v>1132</v>
       </c>
       <c r="P13" t="n">
-        <v>1105</v>
+        <v>1056</v>
       </c>
       <c r="Q13" t="n">
-        <v>856</v>
+        <v>808</v>
       </c>
       <c r="R13" t="n">
-        <v>678</v>
+        <v>637</v>
       </c>
       <c r="S13" t="n">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="T13" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="U13" t="n">
         <v>1993</v>
@@ -1533,25 +1533,25 @@
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
@@ -1612,25 +1612,25 @@
         <v>11</v>
       </c>
       <c r="N15" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O15" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P15" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q15" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R15" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
@@ -1691,25 +1691,25 @@
         <v>909</v>
       </c>
       <c r="N16" t="n">
-        <v>2534</v>
+        <v>2284</v>
       </c>
       <c r="O16" t="n">
-        <v>2175</v>
+        <v>1945</v>
       </c>
       <c r="P16" t="n">
-        <v>2039</v>
+        <v>1819</v>
       </c>
       <c r="Q16" t="n">
-        <v>1576</v>
+        <v>1380</v>
       </c>
       <c r="R16" t="n">
-        <v>1183</v>
+        <v>1018</v>
       </c>
       <c r="S16" t="n">
-        <v>553</v>
+        <v>445</v>
       </c>
       <c r="T16" t="n">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="U16" t="n">
         <v>4083</v>
@@ -1770,25 +1770,25 @@
         <v>359</v>
       </c>
       <c r="N17" t="n">
-        <v>952</v>
+        <v>899</v>
       </c>
       <c r="O17" t="n">
-        <v>801</v>
+        <v>754</v>
       </c>
       <c r="P17" t="n">
-        <v>746</v>
+        <v>702</v>
       </c>
       <c r="Q17" t="n">
-        <v>562</v>
+        <v>529</v>
       </c>
       <c r="R17" t="n">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="S17" t="n">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="T17" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="U17" t="n">
         <v>1672</v>
@@ -1849,25 +1849,25 @@
         <v>2601</v>
       </c>
       <c r="N18" t="n">
-        <v>8714</v>
+        <v>8015</v>
       </c>
       <c r="O18" t="n">
-        <v>7644</v>
+        <v>6990</v>
       </c>
       <c r="P18" t="n">
-        <v>7246</v>
+        <v>6608</v>
       </c>
       <c r="Q18" t="n">
-        <v>5874</v>
+        <v>5300</v>
       </c>
       <c r="R18" t="n">
-        <v>4637</v>
+        <v>4118</v>
       </c>
       <c r="S18" t="n">
-        <v>2439</v>
+        <v>2068</v>
       </c>
       <c r="T18" t="n">
-        <v>766</v>
+        <v>584</v>
       </c>
       <c r="U18" t="n">
         <v>13164</v>
@@ -1928,25 +1928,25 @@
         <v>377</v>
       </c>
       <c r="N19" t="n">
-        <v>2290</v>
+        <v>2155</v>
       </c>
       <c r="O19" t="n">
-        <v>1986</v>
+        <v>1861</v>
       </c>
       <c r="P19" t="n">
-        <v>1909</v>
+        <v>1785</v>
       </c>
       <c r="Q19" t="n">
-        <v>1569</v>
+        <v>1455</v>
       </c>
       <c r="R19" t="n">
-        <v>1262</v>
+        <v>1159</v>
       </c>
       <c r="S19" t="n">
-        <v>676</v>
+        <v>598</v>
       </c>
       <c r="T19" t="n">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="U19" t="n">
         <v>3269</v>
@@ -2165,7 +2165,7 @@
         <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
@@ -2244,25 +2244,25 @@
         <v>49</v>
       </c>
       <c r="N23" t="n">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="O23" t="n">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="P23" t="n">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="Q23" t="n">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="R23" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="S23" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="T23" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="U23" t="n">
         <v>564</v>
@@ -2323,25 +2323,25 @@
         <v>30</v>
       </c>
       <c r="N24" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="O24" t="n">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="P24" t="n">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="Q24" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="R24" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="S24" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="T24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U24" t="n">
         <v>575</v>
@@ -2402,25 +2402,25 @@
         <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="O25" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="P25" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="Q25" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="R25" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="S25" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="T25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U25" t="n">
         <v>373</v>
@@ -2876,16 +2876,16 @@
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O31" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R31" t="n">
         <v>21</v>
@@ -2955,25 +2955,25 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
         <v>24</v>
@@ -3113,25 +3113,25 @@
         <v>349</v>
       </c>
       <c r="N34" t="n">
-        <v>1089</v>
+        <v>1036</v>
       </c>
       <c r="O34" t="n">
-        <v>1071</v>
+        <v>1018</v>
       </c>
       <c r="P34" t="n">
-        <v>1060</v>
+        <v>1007</v>
       </c>
       <c r="Q34" t="n">
-        <v>807</v>
+        <v>759</v>
       </c>
       <c r="R34" t="n">
-        <v>645</v>
+        <v>601</v>
       </c>
       <c r="S34" t="n">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="T34" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="U34" t="n">
         <v>3497</v>
@@ -3192,25 +3192,25 @@
         <v>45</v>
       </c>
       <c r="N35" t="n">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="O35" t="n">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="P35" t="n">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="Q35" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="R35" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="S35" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="T35" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U35" t="n">
         <v>499</v>
@@ -3271,25 +3271,25 @@
         <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O36" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
         <v>58</v>
@@ -4298,22 +4298,22 @@
         <v>8081</v>
       </c>
       <c r="N49" t="n">
-        <v>3179</v>
+        <v>2967</v>
       </c>
       <c r="O49" t="n">
-        <v>1762</v>
+        <v>1651</v>
       </c>
       <c r="P49" t="n">
-        <v>1385</v>
+        <v>1296</v>
       </c>
       <c r="Q49" t="n">
-        <v>681</v>
+        <v>635</v>
       </c>
       <c r="R49" t="n">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="S49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -4377,25 +4377,25 @@
         <v>66</v>
       </c>
       <c r="N50" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O50" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P50" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q50" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R50" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S50" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U50" t="n">
         <v>375</v>
@@ -4456,22 +4456,22 @@
         <v>1022</v>
       </c>
       <c r="N51" t="n">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="O51" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="P51" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="Q51" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="R51" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -4535,25 +4535,25 @@
         <v>32</v>
       </c>
       <c r="N52" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O52" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="P52" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="Q52" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="R52" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="S52" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U52" t="n">
         <v>427</v>
@@ -4614,16 +4614,16 @@
         <v>19</v>
       </c>
       <c r="N53" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P53" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q53" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R53" t="n">
         <v>69</v>
@@ -4772,13 +4772,13 @@
         <v>49</v>
       </c>
       <c r="N55" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="O55" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P55" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q55" t="n">
         <v>36</v>
@@ -4851,22 +4851,22 @@
         <v>10469</v>
       </c>
       <c r="N56" t="n">
-        <v>4345</v>
+        <v>4164</v>
       </c>
       <c r="O56" t="n">
-        <v>2128</v>
+        <v>2036</v>
       </c>
       <c r="P56" t="n">
-        <v>1614</v>
+        <v>1544</v>
       </c>
       <c r="Q56" t="n">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="R56" t="n">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="S56" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -4930,22 +4930,22 @@
         <v>1050</v>
       </c>
       <c r="N57" t="n">
-        <v>2085</v>
+        <v>2047</v>
       </c>
       <c r="O57" t="n">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="P57" t="n">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="Q57" t="n">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="R57" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -5009,19 +5009,19 @@
         <v>35</v>
       </c>
       <c r="N58" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O58" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P58" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q58" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R58" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S58" t="n">
         <v>31</v>
@@ -5325,22 +5325,22 @@
         <v>18</v>
       </c>
       <c r="N62" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O62" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P62" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q62" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R62" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S62" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T62" t="n">
         <v>13</v>
@@ -5562,16 +5562,16 @@
         <v>42</v>
       </c>
       <c r="N65" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O65" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P65" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q65" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R65" t="n">
         <v>149</v>
@@ -5799,22 +5799,22 @@
         <v>131</v>
       </c>
       <c r="N68" t="n">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="O68" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="P68" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="Q68" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R68" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T68" t="n">
         <v>5</v>
@@ -5878,22 +5878,22 @@
         <v>7</v>
       </c>
       <c r="N69" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="O69" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P69" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q69" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R69" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S69" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T69" t="n">
         <v>29</v>
@@ -5957,25 +5957,25 @@
         <v>85</v>
       </c>
       <c r="N70" t="n">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="O70" t="n">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="P70" t="n">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="Q70" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="R70" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="S70" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="T70" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U70" t="n">
         <v>849</v>
@@ -6036,25 +6036,25 @@
         <v>23</v>
       </c>
       <c r="N71" t="n">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="O71" t="n">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="P71" t="n">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="Q71" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="R71" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="S71" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U71" t="n">
         <v>998</v>
@@ -6352,25 +6352,25 @@
         <v>29</v>
       </c>
       <c r="N75" t="n">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="O75" t="n">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="P75" t="n">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="Q75" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="R75" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="S75" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="T75" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="U75" t="n">
         <v>1577</v>
@@ -7063,22 +7063,22 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="O84" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P84" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q84" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="R84" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S84" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="T84" t="n">
         <v>22</v>
@@ -7142,25 +7142,25 @@
         <v>6</v>
       </c>
       <c r="N85" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O85" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P85" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q85" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R85" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S85" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
         <v>259</v>
@@ -7379,7 +7379,7 @@
         <v>239</v>
       </c>
       <c r="N88" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O88" t="n">
         <v>241</v>
@@ -7537,7 +7537,7 @@
         <v>279</v>
       </c>
       <c r="N90" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O90" t="n">
         <v>245</v>
@@ -8327,25 +8327,25 @@
         <v>21</v>
       </c>
       <c r="N100" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="O100" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P100" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q100" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R100" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="S100" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U100" t="n">
         <v>688</v>
@@ -8485,22 +8485,22 @@
         <v>512</v>
       </c>
       <c r="N102" t="n">
-        <v>5664</v>
+        <v>5582</v>
       </c>
       <c r="O102" t="n">
-        <v>3526</v>
+        <v>3459</v>
       </c>
       <c r="P102" t="n">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="Q102" t="n">
-        <v>1521</v>
+        <v>1477</v>
       </c>
       <c r="R102" t="n">
-        <v>812</v>
+        <v>785</v>
       </c>
       <c r="S102" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="T102" t="n">
         <v>11</v>
@@ -8564,16 +8564,16 @@
         <v>52</v>
       </c>
       <c r="N103" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="O103" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="P103" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q103" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R103" t="n">
         <v>71</v>
@@ -8722,13 +8722,13 @@
         <v>10</v>
       </c>
       <c r="N105" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O105" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P105" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q105" t="n">
         <v>81</v>
@@ -8801,25 +8801,25 @@
         <v>75</v>
       </c>
       <c r="N106" t="n">
-        <v>2587</v>
+        <v>2579</v>
       </c>
       <c r="O106" t="n">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="P106" t="n">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="Q106" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="R106" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="S106" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U106" t="n">
         <v>15737</v>
@@ -9117,22 +9117,22 @@
         <v>45</v>
       </c>
       <c r="N110" t="n">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="O110" t="n">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="P110" t="n">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="Q110" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="R110" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T110" t="n">
         <v>1</v>
@@ -9275,22 +9275,22 @@
         <v>269</v>
       </c>
       <c r="N112" t="n">
-        <v>4141</v>
+        <v>4111</v>
       </c>
       <c r="O112" t="n">
-        <v>2252</v>
+        <v>2228</v>
       </c>
       <c r="P112" t="n">
-        <v>1771</v>
+        <v>1748</v>
       </c>
       <c r="Q112" t="n">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="R112" t="n">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="S112" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="T112" t="n">
         <v>5</v>
@@ -9354,19 +9354,19 @@
         <v>57</v>
       </c>
       <c r="N113" t="n">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="O113" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="P113" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Q113" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R113" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S113" t="n">
         <v>11</v>
@@ -9907,25 +9907,25 @@
         <v>86</v>
       </c>
       <c r="N120" t="n">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="O120" t="n">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="P120" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="Q120" t="n">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="R120" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="S120" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="T120" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="U120" t="n">
         <v>1944</v>
@@ -10065,19 +10065,19 @@
         <v>5</v>
       </c>
       <c r="N122" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O122" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P122" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q122" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R122" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -10302,25 +10302,25 @@
         <v>5</v>
       </c>
       <c r="N125" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O125" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P125" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q125" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R125" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S125" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T125" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U125" t="n">
         <v>1001</v>
@@ -10618,25 +10618,25 @@
         <v>129</v>
       </c>
       <c r="N129" t="n">
-        <v>3869</v>
+        <v>3822</v>
       </c>
       <c r="O129" t="n">
-        <v>2369</v>
+        <v>2330</v>
       </c>
       <c r="P129" t="n">
-        <v>2369</v>
+        <v>2330</v>
       </c>
       <c r="Q129" t="n">
-        <v>1705</v>
+        <v>1669</v>
       </c>
       <c r="R129" t="n">
-        <v>1325</v>
+        <v>1293</v>
       </c>
       <c r="S129" t="n">
-        <v>663</v>
+        <v>637</v>
       </c>
       <c r="T129" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="U129" t="n">
         <v>13165</v>
@@ -10697,22 +10697,22 @@
         <v>14</v>
       </c>
       <c r="N130" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O130" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P130" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q130" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R130" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S130" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T130" t="n">
         <v>17</v>
@@ -11171,25 +11171,25 @@
         <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O136" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P136" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q136" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R136" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U136" t="n">
         <v>42</v>
@@ -11250,10 +11250,10 @@
         <v>19</v>
       </c>
       <c r="N137" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="O137" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P137" t="n">
         <v>352</v>
@@ -11882,25 +11882,25 @@
         <v>180</v>
       </c>
       <c r="N145" t="n">
-        <v>3461</v>
+        <v>3430</v>
       </c>
       <c r="O145" t="n">
-        <v>2862</v>
+        <v>2832</v>
       </c>
       <c r="P145" t="n">
-        <v>2654</v>
+        <v>2624</v>
       </c>
       <c r="Q145" t="n">
-        <v>2053</v>
+        <v>2024</v>
       </c>
       <c r="R145" t="n">
-        <v>1578</v>
+        <v>1550</v>
       </c>
       <c r="S145" t="n">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="T145" t="n">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="U145" t="n">
         <v>6627</v>
@@ -11961,25 +11961,25 @@
         <v>78</v>
       </c>
       <c r="N146" t="n">
-        <v>1533</v>
+        <v>1518</v>
       </c>
       <c r="O146" t="n">
-        <v>1298</v>
+        <v>1283</v>
       </c>
       <c r="P146" t="n">
-        <v>1202</v>
+        <v>1188</v>
       </c>
       <c r="Q146" t="n">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="R146" t="n">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="S146" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="T146" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="U146" t="n">
         <v>3016</v>
@@ -12198,7 +12198,7 @@
         <v>2</v>
       </c>
       <c r="N149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O149" t="n">
         <v>4</v>
@@ -12356,19 +12356,19 @@
         <v>246</v>
       </c>
       <c r="N151" t="n">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="O151" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="P151" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Q151" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="R151" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S151" t="n">
         <v>16</v>
@@ -12593,19 +12593,19 @@
         <v>3</v>
       </c>
       <c r="N154" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O154" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P154" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q154" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R154" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S154" t="n">
         <v>17</v>
@@ -12672,25 +12672,25 @@
         <v>8929</v>
       </c>
       <c r="N155" t="n">
-        <v>42648</v>
+        <v>42143</v>
       </c>
       <c r="O155" t="n">
-        <v>24776</v>
+        <v>24383</v>
       </c>
       <c r="P155" t="n">
-        <v>19910</v>
+        <v>19554</v>
       </c>
       <c r="Q155" t="n">
-        <v>10605</v>
+        <v>10352</v>
       </c>
       <c r="R155" t="n">
-        <v>6348</v>
+        <v>6155</v>
       </c>
       <c r="S155" t="n">
-        <v>2140</v>
+        <v>2048</v>
       </c>
       <c r="T155" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="U155" t="n">
         <v>208992</v>
@@ -12751,22 +12751,22 @@
         <v>422</v>
       </c>
       <c r="N156" t="n">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="O156" t="n">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="P156" t="n">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q156" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="R156" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="S156" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="T156" t="n">
         <v>8</v>
@@ -12909,7 +12909,7 @@
         <v>5</v>
       </c>
       <c r="N158" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O158" t="n">
         <v>29</v>
@@ -14643,22 +14643,22 @@
         <v>3</v>
       </c>
       <c r="N180" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O180" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P180" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q180" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R180" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S180" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T180" t="n">
         <v>9</v>
@@ -15589,25 +15589,25 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P7" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R7" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S7" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V7" t="n">
         <v>1001</v>
@@ -16009,25 +16009,25 @@
         <v>86</v>
       </c>
       <c r="O12" t="n">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="P12" t="n">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="Q12" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="R12" t="n">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="S12" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="T12" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="U12" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="V12" t="n">
         <v>1944</v>
@@ -16177,19 +16177,19 @@
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T14" t="n">
         <v>15</v>
@@ -16345,25 +16345,25 @@
         <v>129</v>
       </c>
       <c r="O16" t="n">
-        <v>3869</v>
+        <v>3822</v>
       </c>
       <c r="P16" t="n">
-        <v>2369</v>
+        <v>2330</v>
       </c>
       <c r="Q16" t="n">
-        <v>2369</v>
+        <v>2330</v>
       </c>
       <c r="R16" t="n">
-        <v>1705</v>
+        <v>1669</v>
       </c>
       <c r="S16" t="n">
-        <v>1325</v>
+        <v>1293</v>
       </c>
       <c r="T16" t="n">
-        <v>663</v>
+        <v>637</v>
       </c>
       <c r="U16" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="V16" t="n">
         <v>13165</v>
@@ -16429,22 +16429,22 @@
         <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P17" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q17" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R17" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="S17" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T17" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U17" t="n">
         <v>15</v>
@@ -16723,25 +16723,25 @@
         <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="P2" t="n">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="Q2" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="R2" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="T2" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
         <v>331</v>
@@ -16807,25 +16807,25 @@
         <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
         <v>48</v>
@@ -16975,25 +16975,25 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>55</v>
@@ -17143,25 +17143,25 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V7" t="n">
         <v>60</v>
@@ -17227,25 +17227,25 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V8" t="n">
         <v>60</v>
@@ -17395,25 +17395,25 @@
         <v>905</v>
       </c>
       <c r="O10" t="n">
-        <v>2520</v>
+        <v>2272</v>
       </c>
       <c r="P10" t="n">
-        <v>2166</v>
+        <v>1938</v>
       </c>
       <c r="Q10" t="n">
-        <v>2030</v>
+        <v>1812</v>
       </c>
       <c r="R10" t="n">
-        <v>1572</v>
+        <v>1378</v>
       </c>
       <c r="S10" t="n">
-        <v>1180</v>
+        <v>1016</v>
       </c>
       <c r="T10" t="n">
-        <v>553</v>
+        <v>445</v>
       </c>
       <c r="U10" t="n">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="V10" t="n">
         <v>4064</v>
@@ -17479,25 +17479,25 @@
         <v>90</v>
       </c>
       <c r="O11" t="n">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="P11" t="n">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="n">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="R11" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="S11" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="T11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="V11" t="n">
         <v>383</v>
@@ -17563,25 +17563,25 @@
         <v>2601</v>
       </c>
       <c r="O12" t="n">
-        <v>8714</v>
+        <v>8015</v>
       </c>
       <c r="P12" t="n">
-        <v>7644</v>
+        <v>6990</v>
       </c>
       <c r="Q12" t="n">
-        <v>7246</v>
+        <v>6608</v>
       </c>
       <c r="R12" t="n">
-        <v>5874</v>
+        <v>5300</v>
       </c>
       <c r="S12" t="n">
-        <v>4637</v>
+        <v>4118</v>
       </c>
       <c r="T12" t="n">
-        <v>2439</v>
+        <v>2068</v>
       </c>
       <c r="U12" t="n">
-        <v>766</v>
+        <v>584</v>
       </c>
       <c r="V12" t="n">
         <v>13164</v>
@@ -17731,16 +17731,16 @@
         <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P14" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q14" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R14" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S14" t="n">
         <v>106</v>
@@ -18319,25 +18319,25 @@
         <v>57</v>
       </c>
       <c r="O21" t="n">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="P21" t="n">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="Q21" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="R21" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="S21" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="T21" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V21" t="n">
         <v>414</v>
@@ -18403,25 +18403,25 @@
         <v>22</v>
       </c>
       <c r="O22" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="P22" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q22" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R22" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="S22" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="T22" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
         <v>163</v>
@@ -18487,22 +18487,22 @@
         <v>15</v>
       </c>
       <c r="O23" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P23" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="Q23" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="R23" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="S23" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="T23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -18571,25 +18571,25 @@
         <v>109</v>
       </c>
       <c r="O24" t="n">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="P24" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
       <c r="Q24" t="n">
-        <v>438</v>
+        <v>395</v>
       </c>
       <c r="R24" t="n">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="S24" t="n">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="T24" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="U24" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="V24" t="n">
         <v>706</v>
@@ -18655,22 +18655,22 @@
         <v>15</v>
       </c>
       <c r="O25" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P25" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q25" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="R25" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="S25" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="T25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U25" t="n">
         <v>4</v>
@@ -18739,25 +18739,25 @@
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P26" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q26" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R26" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S26" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V26" t="n">
         <v>224</v>
@@ -18823,25 +18823,25 @@
         <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>17</v>
@@ -18907,25 +18907,25 @@
         <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>17</v>
@@ -18991,25 +18991,25 @@
         <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
         <v>58</v>
@@ -19075,22 +19075,22 @@
         <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q30" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="R30" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="S30" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="T30" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="U30" t="n">
         <v>5</v>
@@ -19159,22 +19159,22 @@
         <v>16</v>
       </c>
       <c r="O31" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="P31" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="Q31" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="R31" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="S31" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U31" t="n">
         <v>17</v>
@@ -19243,25 +19243,25 @@
         <v>20</v>
       </c>
       <c r="O32" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P32" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="Q32" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="R32" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="S32" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="T32" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="U32" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V32" t="n">
         <v>100</v>
@@ -19411,25 +19411,25 @@
         <v>75</v>
       </c>
       <c r="O34" t="n">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="P34" t="n">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="Q34" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="R34" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="S34" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="T34" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="U34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V34" t="n">
         <v>323</v>
@@ -19495,25 +19495,25 @@
         <v>144</v>
       </c>
       <c r="O35" t="n">
-        <v>806</v>
+        <v>750</v>
       </c>
       <c r="P35" t="n">
-        <v>728</v>
+        <v>678</v>
       </c>
       <c r="Q35" t="n">
-        <v>699</v>
+        <v>649</v>
       </c>
       <c r="R35" t="n">
-        <v>607</v>
+        <v>560</v>
       </c>
       <c r="S35" t="n">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="T35" t="n">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="U35" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="V35" t="n">
         <v>1103</v>
@@ -19663,25 +19663,25 @@
         <v>37</v>
       </c>
       <c r="O37" t="n">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="P37" t="n">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q37" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R37" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T37" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>446</v>
@@ -19747,25 +19747,25 @@
         <v>26</v>
       </c>
       <c r="O38" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P38" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Q38" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="R38" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="S38" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="T38" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="U38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V38" t="n">
         <v>593</v>
@@ -20335,7 +20335,7 @@
         <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P45" t="n">
         <v>11</v>
@@ -20419,25 +20419,25 @@
         <v>49</v>
       </c>
       <c r="O46" t="n">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="P46" t="n">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="Q46" t="n">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="R46" t="n">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="S46" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="T46" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="U46" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="V46" t="n">
         <v>564</v>
@@ -20503,25 +20503,25 @@
         <v>25</v>
       </c>
       <c r="O47" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="P47" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Q47" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="R47" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="S47" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="T47" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V47" t="n">
         <v>373</v>
@@ -20587,19 +20587,19 @@
         <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -20671,22 +20671,22 @@
         <v>176</v>
       </c>
       <c r="O49" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="P49" t="n">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="R49" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="S49" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T49" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U49" t="n">
         <v>4</v>
@@ -21301,25 +21301,25 @@
         <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P2" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q2" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R2" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V2" t="n">
         <v>324</v>
@@ -21385,25 +21385,25 @@
         <v>32</v>
       </c>
       <c r="O3" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="P3" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="Q3" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="R3" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="S3" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="T3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="U3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
         <v>427</v>
@@ -21469,16 +21469,16 @@
         <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -21637,22 +21637,22 @@
         <v>8081</v>
       </c>
       <c r="O6" t="n">
-        <v>3179</v>
+        <v>2967</v>
       </c>
       <c r="P6" t="n">
-        <v>1762</v>
+        <v>1651</v>
       </c>
       <c r="Q6" t="n">
-        <v>1385</v>
+        <v>1296</v>
       </c>
       <c r="R6" t="n">
-        <v>681</v>
+        <v>635</v>
       </c>
       <c r="S6" t="n">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="T6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -21721,22 +21721,22 @@
         <v>1022</v>
       </c>
       <c r="O7" t="n">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="P7" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="Q7" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="R7" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="S7" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -21889,13 +21889,13 @@
         <v>49</v>
       </c>
       <c r="O9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P9" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R9" t="n">
         <v>36</v>
@@ -21973,22 +21973,22 @@
         <v>10469</v>
       </c>
       <c r="O10" t="n">
-        <v>4345</v>
+        <v>4164</v>
       </c>
       <c r="P10" t="n">
-        <v>2128</v>
+        <v>2036</v>
       </c>
       <c r="Q10" t="n">
-        <v>1614</v>
+        <v>1544</v>
       </c>
       <c r="R10" t="n">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="S10" t="n">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="T10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -22057,22 +22057,22 @@
         <v>1050</v>
       </c>
       <c r="O11" t="n">
-        <v>2085</v>
+        <v>2047</v>
       </c>
       <c r="P11" t="n">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="Q11" t="n">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="R11" t="n">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="S11" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -22309,16 +22309,16 @@
         <v>19</v>
       </c>
       <c r="O14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q14" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S14" t="n">
         <v>69</v>
@@ -23695,16 +23695,16 @@
         <v>42</v>
       </c>
       <c r="O16" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P16" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q16" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R16" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S16" t="n">
         <v>149</v>
@@ -23779,22 +23779,22 @@
         <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
@@ -25123,19 +25123,19 @@
         <v>35</v>
       </c>
       <c r="O33" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P33" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q33" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R33" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S33" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T33" t="n">
         <v>31</v>
@@ -25207,22 +25207,22 @@
         <v>18</v>
       </c>
       <c r="O34" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P34" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q34" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R34" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S34" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T34" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U34" t="n">
         <v>13</v>
@@ -25543,22 +25543,22 @@
         <v>131</v>
       </c>
       <c r="O38" t="n">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="P38" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="Q38" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="R38" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="S38" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="T38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U38" t="n">
         <v>5</v>
@@ -25711,25 +25711,25 @@
         <v>85</v>
       </c>
       <c r="O40" t="n">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="P40" t="n">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="Q40" t="n">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="R40" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="S40" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="T40" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="U40" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V40" t="n">
         <v>849</v>
@@ -25795,25 +25795,25 @@
         <v>23</v>
       </c>
       <c r="O41" t="n">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="P41" t="n">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="Q41" t="n">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="R41" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="S41" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="T41" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U41" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V41" t="n">
         <v>941</v>
@@ -26677,22 +26677,22 @@
         <v>11</v>
       </c>
       <c r="O4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>1</v>
@@ -26929,7 +26929,7 @@
         <v>59</v>
       </c>
       <c r="O7" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P7" t="n">
         <v>114</v>
@@ -27013,7 +27013,7 @@
         <v>279</v>
       </c>
       <c r="O8" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P8" t="n">
         <v>245</v>
@@ -27601,25 +27601,25 @@
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P15" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q15" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
         <v>206</v>
@@ -28903,13 +28903,13 @@
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P2" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R2" t="n">
         <v>81</v>
@@ -28987,25 +28987,25 @@
         <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="P3" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="Q3" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="R3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="T3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>688</v>
@@ -29239,22 +29239,22 @@
         <v>512</v>
       </c>
       <c r="O6" t="n">
-        <v>5664</v>
+        <v>5582</v>
       </c>
       <c r="P6" t="n">
-        <v>3526</v>
+        <v>3459</v>
       </c>
       <c r="Q6" t="n">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="R6" t="n">
-        <v>1521</v>
+        <v>1477</v>
       </c>
       <c r="S6" t="n">
-        <v>812</v>
+        <v>785</v>
       </c>
       <c r="T6" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="U6" t="n">
         <v>11</v>
@@ -29323,16 +29323,16 @@
         <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="P7" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="Q7" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="R7" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S7" t="n">
         <v>71</v>
@@ -29491,25 +29491,25 @@
         <v>75</v>
       </c>
       <c r="O9" t="n">
-        <v>2587</v>
+        <v>2579</v>
       </c>
       <c r="P9" t="n">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="Q9" t="n">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="R9" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="S9" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="T9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>15737</v>
@@ -29743,22 +29743,22 @@
         <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="P12" t="n">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="Q12" t="n">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="R12" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -29911,22 +29911,22 @@
         <v>269</v>
       </c>
       <c r="O14" t="n">
-        <v>4141</v>
+        <v>4111</v>
       </c>
       <c r="P14" t="n">
-        <v>2252</v>
+        <v>2228</v>
       </c>
       <c r="Q14" t="n">
-        <v>1771</v>
+        <v>1748</v>
       </c>
       <c r="R14" t="n">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="S14" t="n">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
         <v>5</v>
@@ -29995,19 +29995,19 @@
         <v>57</v>
       </c>
       <c r="O15" t="n">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="P15" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="Q15" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="R15" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T15" t="n">
         <v>11</v>
@@ -30709,7 +30709,7 @@
         <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
         <v>17</v>
@@ -31129,19 +31129,19 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
         <v>17</v>
@@ -31801,10 +31801,10 @@
         <v>13</v>
       </c>
       <c r="O18" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P18" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q18" t="n">
         <v>181</v>
@@ -31885,25 +31885,25 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>42</v>
@@ -32389,25 +32389,25 @@
         <v>180</v>
       </c>
       <c r="O25" t="n">
-        <v>3461</v>
+        <v>3430</v>
       </c>
       <c r="P25" t="n">
-        <v>2862</v>
+        <v>2832</v>
       </c>
       <c r="Q25" t="n">
-        <v>2654</v>
+        <v>2624</v>
       </c>
       <c r="R25" t="n">
-        <v>2053</v>
+        <v>2024</v>
       </c>
       <c r="S25" t="n">
-        <v>1578</v>
+        <v>1550</v>
       </c>
       <c r="T25" t="n">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="U25" t="n">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="V25" t="n">
         <v>6627</v>
@@ -32473,25 +32473,25 @@
         <v>78</v>
       </c>
       <c r="O26" t="n">
-        <v>1533</v>
+        <v>1518</v>
       </c>
       <c r="P26" t="n">
-        <v>1298</v>
+        <v>1283</v>
       </c>
       <c r="Q26" t="n">
-        <v>1202</v>
+        <v>1188</v>
       </c>
       <c r="R26" t="n">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="S26" t="n">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="T26" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="U26" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="V26" t="n">
         <v>3016</v>
@@ -32641,7 +32641,7 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
         <v>4</v>
@@ -32725,19 +32725,19 @@
         <v>246</v>
       </c>
       <c r="O29" t="n">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="P29" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="Q29" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="R29" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="S29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T29" t="n">
         <v>16</v>
@@ -32893,25 +32893,25 @@
         <v>8929</v>
       </c>
       <c r="O31" t="n">
-        <v>42648</v>
+        <v>42143</v>
       </c>
       <c r="P31" t="n">
-        <v>24776</v>
+        <v>24383</v>
       </c>
       <c r="Q31" t="n">
-        <v>19910</v>
+        <v>19554</v>
       </c>
       <c r="R31" t="n">
-        <v>10605</v>
+        <v>10352</v>
       </c>
       <c r="S31" t="n">
-        <v>6348</v>
+        <v>6155</v>
       </c>
       <c r="T31" t="n">
-        <v>2140</v>
+        <v>2048</v>
       </c>
       <c r="U31" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="V31" t="n">
         <v>208992</v>
@@ -32977,22 +32977,22 @@
         <v>422</v>
       </c>
       <c r="O32" t="n">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="P32" t="n">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="Q32" t="n">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="R32" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="S32" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="T32" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="U32" t="n">
         <v>8</v>
